--- a/Data/EXCEL/Transfer/salemon/202512/7722-salemon-202512.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202512/7722-salemon-202512.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\202512\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202512\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1BEBEB2-7357-4C29-94D4-B3869E5E093B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2F134F0-D6CF-4719-9018-E4733ECD8BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="930" windowWidth="26910" windowHeight="18975" xr2:uid="{BEA43B23-2441-49DC-B76C-1857FD8B8E64}"/>
+    <workbookView xWindow="0" yWindow="1740" windowWidth="17565" windowHeight="11295" xr2:uid="{DD98271A-0C8A-490B-9A0E-8AB36D7A8FB2}"/>
   </bookViews>
   <sheets>
     <sheet name="7722-salemon-202512" sheetId="2" r:id="rId1"/>
@@ -261,7 +261,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -277,7 +277,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -857,13 +857,13 @@
     <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1258,20 +1258,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA719A5-B8A9-48C2-9968-AD39F22DD1EA}">
-  <dimension ref="A1:Q29"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{343958A7-FFDA-4E08-8C53-BFCD8D53B401}">
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.125" customWidth="1"/>
-    <col min="2" max="2" width="12.125" customWidth="1"/>
-    <col min="3" max="3" width="12.75" customWidth="1"/>
-    <col min="4" max="5" width="12.125" customWidth="1"/>
-    <col min="6" max="6" width="12.75" customWidth="1"/>
-    <col min="7" max="7" width="13.875" customWidth="1"/>
-    <col min="8" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="12.75" customWidth="1"/>
-    <col min="12" max="15" width="12.125" customWidth="1"/>
-    <col min="16" max="17" width="12.75" customWidth="1"/>
+    <col min="1" max="1" width="9.375" customWidth="1"/>
+    <col min="2" max="2" width="7.5" customWidth="1"/>
+    <col min="3" max="3" width="7.875" customWidth="1"/>
+    <col min="4" max="5" width="7.5" customWidth="1"/>
+    <col min="6" max="6" width="7.875" customWidth="1"/>
+    <col min="7" max="7" width="8.625" customWidth="1"/>
+    <col min="8" max="10" width="7.5" customWidth="1"/>
+    <col min="11" max="11" width="7.875" customWidth="1"/>
+    <col min="12" max="15" width="7.5" customWidth="1"/>
+    <col min="16" max="16" width="7.875" customWidth="1"/>
+    <col min="17" max="17" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1424,696 +1425,696 @@
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B5" s="6">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C5" s="6">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="D5" s="6">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="E5" s="6">
-        <v>522</v>
+        <v>550</v>
       </c>
       <c r="F5" s="7">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="7">
-        <v>-0.88</v>
+        <v>0.71</v>
       </c>
       <c r="H5" s="8">
-        <v>7.57</v>
+        <v>7.18</v>
       </c>
       <c r="I5" s="9">
-        <v>7.58</v>
-      </c>
-      <c r="J5" s="9">
-        <v>27.8</v>
+        <v>-5.18</v>
+      </c>
+      <c r="J5" s="7">
+        <v>16.3</v>
       </c>
       <c r="K5" s="8">
-        <v>71.540000000000006</v>
-      </c>
-      <c r="L5" s="9">
-        <v>26</v>
+        <v>78.72</v>
+      </c>
+      <c r="L5" s="7">
+        <v>25</v>
       </c>
       <c r="M5" s="8">
-        <v>7.57</v>
+        <v>7.18</v>
       </c>
       <c r="N5" s="9">
-        <v>7.58</v>
-      </c>
-      <c r="O5" s="9">
-        <v>27.8</v>
+        <v>-5.18</v>
+      </c>
+      <c r="O5" s="7">
+        <v>16.3</v>
       </c>
       <c r="P5" s="8">
-        <v>71.540000000000006</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>26</v>
+        <v>78.72</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B6" s="12">
-        <v>601</v>
+        <v>569</v>
       </c>
       <c r="C6" s="12">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="D6" s="12">
-        <v>609</v>
+        <v>591</v>
       </c>
       <c r="E6" s="12">
-        <v>554</v>
+        <v>522</v>
       </c>
       <c r="F6" s="13">
-        <v>-35</v>
+        <v>-5</v>
       </c>
       <c r="G6" s="13">
-        <v>-5.78</v>
+        <v>-0.88</v>
       </c>
       <c r="H6" s="14">
-        <v>7.04</v>
+        <v>7.57</v>
       </c>
       <c r="I6" s="15">
-        <v>3.66</v>
+        <v>7.58</v>
       </c>
       <c r="J6" s="15">
-        <v>26.4</v>
+        <v>27.8</v>
       </c>
       <c r="K6" s="14">
-        <v>63.97</v>
+        <v>71.540000000000006</v>
       </c>
       <c r="L6" s="15">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="M6" s="14">
-        <v>7.04</v>
+        <v>7.57</v>
       </c>
       <c r="N6" s="15">
-        <v>3.66</v>
+        <v>7.58</v>
       </c>
       <c r="O6" s="15">
-        <v>26.4</v>
+        <v>27.8</v>
       </c>
       <c r="P6" s="14">
-        <v>63.97</v>
+        <v>71.540000000000006</v>
       </c>
       <c r="Q6" s="15">
-        <v>25.8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B7" s="6">
-        <v>619</v>
+        <v>601</v>
       </c>
       <c r="C7" s="6">
-        <v>606</v>
+        <v>571</v>
       </c>
       <c r="D7" s="6">
-        <v>643</v>
+        <v>609</v>
       </c>
       <c r="E7" s="6">
-        <v>580</v>
-      </c>
-      <c r="F7" s="7">
-        <v>-7</v>
-      </c>
-      <c r="G7" s="7">
-        <v>-1.1399999999999999</v>
+        <v>554</v>
+      </c>
+      <c r="F7" s="9">
+        <v>-35</v>
+      </c>
+      <c r="G7" s="9">
+        <v>-5.78</v>
       </c>
       <c r="H7" s="8">
-        <v>6.79</v>
+        <v>7.04</v>
       </c>
       <c r="I7" s="7">
-        <v>-2.4700000000000002</v>
-      </c>
-      <c r="J7" s="9">
-        <v>24.4</v>
+        <v>3.66</v>
+      </c>
+      <c r="J7" s="7">
+        <v>26.4</v>
       </c>
       <c r="K7" s="8">
-        <v>56.94</v>
-      </c>
-      <c r="L7" s="9">
-        <v>25.7</v>
+        <v>63.97</v>
+      </c>
+      <c r="L7" s="7">
+        <v>25.8</v>
       </c>
       <c r="M7" s="8">
-        <v>6.79</v>
+        <v>7.04</v>
       </c>
       <c r="N7" s="7">
-        <v>-2.4700000000000002</v>
-      </c>
-      <c r="O7" s="9">
-        <v>24.4</v>
+        <v>3.66</v>
+      </c>
+      <c r="O7" s="7">
+        <v>26.4</v>
       </c>
       <c r="P7" s="8">
-        <v>56.94</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>25.7</v>
+        <v>63.97</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>25.8</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B8" s="12">
-        <v>710</v>
+        <v>619</v>
       </c>
       <c r="C8" s="12">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="D8" s="12">
-        <v>764</v>
+        <v>643</v>
       </c>
       <c r="E8" s="12">
-        <v>611</v>
+        <v>580</v>
       </c>
       <c r="F8" s="13">
-        <v>-106</v>
+        <v>-7</v>
       </c>
       <c r="G8" s="13">
-        <v>-14.74</v>
+        <v>-1.1399999999999999</v>
       </c>
       <c r="H8" s="14">
-        <v>6.96</v>
-      </c>
-      <c r="I8" s="15">
-        <v>8.69</v>
+        <v>6.79</v>
+      </c>
+      <c r="I8" s="13">
+        <v>-2.4700000000000002</v>
       </c>
       <c r="J8" s="15">
-        <v>30.8</v>
+        <v>24.4</v>
       </c>
       <c r="K8" s="14">
-        <v>50.15</v>
+        <v>56.94</v>
       </c>
       <c r="L8" s="15">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="M8" s="14">
-        <v>6.96</v>
-      </c>
-      <c r="N8" s="15">
-        <v>8.69</v>
+        <v>6.79</v>
+      </c>
+      <c r="N8" s="13">
+        <v>-2.4700000000000002</v>
       </c>
       <c r="O8" s="15">
-        <v>30.8</v>
+        <v>24.4</v>
       </c>
       <c r="P8" s="14">
-        <v>50.15</v>
+        <v>56.94</v>
       </c>
       <c r="Q8" s="15">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B9" s="6">
-        <v>737</v>
+        <v>710</v>
       </c>
       <c r="C9" s="6">
-        <v>719</v>
+        <v>613</v>
       </c>
       <c r="D9" s="6">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="E9" s="6">
-        <v>660</v>
-      </c>
-      <c r="F9" s="7">
-        <v>-13</v>
-      </c>
-      <c r="G9" s="7">
-        <v>-1.78</v>
+        <v>611</v>
+      </c>
+      <c r="F9" s="9">
+        <v>-106</v>
+      </c>
+      <c r="G9" s="9">
+        <v>-14.74</v>
       </c>
       <c r="H9" s="8">
-        <v>6.4</v>
-      </c>
-      <c r="I9" s="9">
-        <v>0.74</v>
-      </c>
-      <c r="J9" s="9">
-        <v>23.9</v>
+        <v>6.96</v>
+      </c>
+      <c r="I9" s="7">
+        <v>8.69</v>
+      </c>
+      <c r="J9" s="7">
+        <v>30.8</v>
       </c>
       <c r="K9" s="8">
-        <v>43.19</v>
-      </c>
-      <c r="L9" s="9">
-        <v>25.1</v>
+        <v>50.15</v>
+      </c>
+      <c r="L9" s="7">
+        <v>25.9</v>
       </c>
       <c r="M9" s="8">
-        <v>6.4</v>
-      </c>
-      <c r="N9" s="9">
-        <v>0.74</v>
-      </c>
-      <c r="O9" s="9">
-        <v>23.9</v>
+        <v>6.96</v>
+      </c>
+      <c r="N9" s="7">
+        <v>8.69</v>
+      </c>
+      <c r="O9" s="7">
+        <v>30.8</v>
       </c>
       <c r="P9" s="8">
-        <v>43.19</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>25.1</v>
+        <v>50.15</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>25.9</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B10" s="12">
-        <v>598</v>
+        <v>737</v>
       </c>
       <c r="C10" s="12">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="D10" s="12">
-        <v>795</v>
+        <v>752</v>
       </c>
       <c r="E10" s="12">
-        <v>546</v>
-      </c>
-      <c r="F10" s="15">
-        <v>133</v>
-      </c>
-      <c r="G10" s="15">
-        <v>22.2</v>
+        <v>660</v>
+      </c>
+      <c r="F10" s="13">
+        <v>-13</v>
+      </c>
+      <c r="G10" s="13">
+        <v>-1.78</v>
       </c>
       <c r="H10" s="14">
-        <v>6.36</v>
-      </c>
-      <c r="I10" s="13">
-        <v>-0.28999999999999998</v>
+        <v>6.4</v>
+      </c>
+      <c r="I10" s="15">
+        <v>0.74</v>
       </c>
       <c r="J10" s="15">
-        <v>15</v>
+        <v>23.9</v>
       </c>
       <c r="K10" s="14">
-        <v>36.79</v>
+        <v>43.19</v>
       </c>
       <c r="L10" s="15">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="M10" s="14">
-        <v>6.36</v>
-      </c>
-      <c r="N10" s="13">
-        <v>-0.28999999999999998</v>
+        <v>6.4</v>
+      </c>
+      <c r="N10" s="15">
+        <v>0.74</v>
       </c>
       <c r="O10" s="15">
-        <v>15</v>
+        <v>23.9</v>
       </c>
       <c r="P10" s="14">
-        <v>36.79</v>
+        <v>43.19</v>
       </c>
       <c r="Q10" s="15">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B11" s="6">
-        <v>617</v>
+        <v>598</v>
       </c>
       <c r="C11" s="6">
-        <v>599</v>
+        <v>732</v>
       </c>
       <c r="D11" s="6">
-        <v>649</v>
+        <v>795</v>
       </c>
       <c r="E11" s="6">
-        <v>582</v>
+        <v>546</v>
       </c>
       <c r="F11" s="7">
-        <v>-13</v>
+        <v>133</v>
       </c>
       <c r="G11" s="7">
-        <v>-2.12</v>
+        <v>22.2</v>
       </c>
       <c r="H11" s="8">
-        <v>6.37</v>
+        <v>6.36</v>
       </c>
       <c r="I11" s="9">
-        <v>8.09</v>
-      </c>
-      <c r="J11" s="9">
-        <v>33.1</v>
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="J11" s="7">
+        <v>15</v>
       </c>
       <c r="K11" s="8">
-        <v>30.43</v>
-      </c>
-      <c r="L11" s="9">
-        <v>27.7</v>
+        <v>36.79</v>
+      </c>
+      <c r="L11" s="7">
+        <v>25.3</v>
       </c>
       <c r="M11" s="8">
-        <v>6.37</v>
+        <v>6.36</v>
       </c>
       <c r="N11" s="9">
-        <v>8.09</v>
-      </c>
-      <c r="O11" s="9">
-        <v>33.1</v>
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="O11" s="7">
+        <v>15</v>
       </c>
       <c r="P11" s="8">
-        <v>30.43</v>
-      </c>
-      <c r="Q11" s="9">
-        <v>27.7</v>
+        <v>36.79</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>25.3</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B12" s="12">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="C12" s="12">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="D12" s="12">
-        <v>664</v>
+        <v>649</v>
       </c>
       <c r="E12" s="12">
-        <v>471</v>
+        <v>582</v>
       </c>
       <c r="F12" s="13">
-        <v>-18</v>
+        <v>-13</v>
       </c>
       <c r="G12" s="13">
-        <v>-2.86</v>
+        <v>-2.12</v>
       </c>
       <c r="H12" s="14">
-        <v>5.9</v>
-      </c>
-      <c r="I12" s="13">
-        <v>-2.99</v>
+        <v>6.37</v>
+      </c>
+      <c r="I12" s="15">
+        <v>8.09</v>
       </c>
       <c r="J12" s="15">
-        <v>32.9</v>
+        <v>33.1</v>
       </c>
       <c r="K12" s="14">
-        <v>24.06</v>
+        <v>30.43</v>
       </c>
       <c r="L12" s="15">
-        <v>26.4</v>
+        <v>27.7</v>
       </c>
       <c r="M12" s="14">
-        <v>5.9</v>
-      </c>
-      <c r="N12" s="13">
-        <v>-2.99</v>
+        <v>6.37</v>
+      </c>
+      <c r="N12" s="15">
+        <v>8.09</v>
       </c>
       <c r="O12" s="15">
-        <v>32.9</v>
+        <v>33.1</v>
       </c>
       <c r="P12" s="14">
-        <v>24.06</v>
+        <v>30.43</v>
       </c>
       <c r="Q12" s="15">
-        <v>26.4</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B13" s="6">
-        <v>764</v>
+        <v>610</v>
       </c>
       <c r="C13" s="6">
-        <v>630</v>
+        <v>612</v>
       </c>
       <c r="D13" s="6">
-        <v>828</v>
+        <v>664</v>
       </c>
       <c r="E13" s="6">
-        <v>617</v>
-      </c>
-      <c r="F13" s="7">
-        <v>-139</v>
-      </c>
-      <c r="G13" s="7">
-        <v>-18.079999999999998</v>
+        <v>471</v>
+      </c>
+      <c r="F13" s="9">
+        <v>-18</v>
+      </c>
+      <c r="G13" s="9">
+        <v>-2.86</v>
       </c>
       <c r="H13" s="8">
-        <v>6.08</v>
+        <v>5.9</v>
       </c>
       <c r="I13" s="9">
-        <v>4</v>
-      </c>
-      <c r="J13" s="9">
-        <v>25.4</v>
+        <v>-2.99</v>
+      </c>
+      <c r="J13" s="7">
+        <v>32.9</v>
       </c>
       <c r="K13" s="8">
-        <v>18.16</v>
-      </c>
-      <c r="L13" s="9">
-        <v>24.4</v>
+        <v>24.06</v>
+      </c>
+      <c r="L13" s="7">
+        <v>26.4</v>
       </c>
       <c r="M13" s="8">
-        <v>6.08</v>
+        <v>5.9</v>
       </c>
       <c r="N13" s="9">
-        <v>4</v>
-      </c>
-      <c r="O13" s="9">
-        <v>25.4</v>
+        <v>-2.99</v>
+      </c>
+      <c r="O13" s="7">
+        <v>32.9</v>
       </c>
       <c r="P13" s="8">
-        <v>18.16</v>
-      </c>
-      <c r="Q13" s="9">
-        <v>24.4</v>
+        <v>24.06</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>26.4</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B14" s="12">
-        <v>730</v>
+        <v>764</v>
       </c>
       <c r="C14" s="12">
-        <v>769</v>
+        <v>630</v>
       </c>
       <c r="D14" s="12">
-        <v>934</v>
+        <v>828</v>
       </c>
       <c r="E14" s="12">
-        <v>711</v>
-      </c>
-      <c r="F14" s="15">
-        <v>26</v>
-      </c>
-      <c r="G14" s="15">
-        <v>3.5</v>
+        <v>617</v>
+      </c>
+      <c r="F14" s="13">
+        <v>-139</v>
+      </c>
+      <c r="G14" s="13">
+        <v>-18.079999999999998</v>
       </c>
       <c r="H14" s="14">
-        <v>5.85</v>
-      </c>
-      <c r="I14" s="13">
-        <v>-6.22</v>
+        <v>6.08</v>
+      </c>
+      <c r="I14" s="15">
+        <v>4</v>
       </c>
       <c r="J14" s="15">
-        <v>24.2</v>
+        <v>25.4</v>
       </c>
       <c r="K14" s="14">
-        <v>12.08</v>
+        <v>18.16</v>
       </c>
       <c r="L14" s="15">
-        <v>23.9</v>
+        <v>24.4</v>
       </c>
       <c r="M14" s="14">
-        <v>5.85</v>
-      </c>
-      <c r="N14" s="13">
-        <v>-6.22</v>
+        <v>6.08</v>
+      </c>
+      <c r="N14" s="15">
+        <v>4</v>
       </c>
       <c r="O14" s="15">
-        <v>24.2</v>
+        <v>25.4</v>
       </c>
       <c r="P14" s="14">
-        <v>12.08</v>
+        <v>18.16</v>
       </c>
       <c r="Q14" s="15">
-        <v>23.9</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B15" s="6">
-        <v>461</v>
+        <v>730</v>
       </c>
       <c r="C15" s="6">
-        <v>743</v>
+        <v>769</v>
       </c>
       <c r="D15" s="6">
-        <v>748</v>
+        <v>934</v>
       </c>
       <c r="E15" s="6">
-        <v>460</v>
-      </c>
-      <c r="F15" s="9">
-        <v>283.5</v>
-      </c>
-      <c r="G15" s="9">
-        <v>61.7</v>
+        <v>711</v>
+      </c>
+      <c r="F15" s="7">
+        <v>26</v>
+      </c>
+      <c r="G15" s="7">
+        <v>3.5</v>
       </c>
       <c r="H15" s="8">
-        <v>6.23</v>
+        <v>5.85</v>
       </c>
       <c r="I15" s="9">
-        <v>0.99</v>
-      </c>
-      <c r="J15" s="9">
-        <v>23.5</v>
+        <v>-6.22</v>
+      </c>
+      <c r="J15" s="7">
+        <v>24.2</v>
       </c>
       <c r="K15" s="8">
-        <v>6.23</v>
-      </c>
-      <c r="L15" s="9">
-        <v>23.5</v>
+        <v>12.08</v>
+      </c>
+      <c r="L15" s="7">
+        <v>23.9</v>
       </c>
       <c r="M15" s="8">
-        <v>6.23</v>
+        <v>5.85</v>
       </c>
       <c r="N15" s="9">
-        <v>0.99</v>
-      </c>
-      <c r="O15" s="9">
-        <v>23.5</v>
+        <v>-6.22</v>
+      </c>
+      <c r="O15" s="7">
+        <v>24.2</v>
       </c>
       <c r="P15" s="8">
-        <v>6.23</v>
-      </c>
-      <c r="Q15" s="9">
-        <v>23.5</v>
+        <v>12.08</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>23.9</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="B16" s="12">
-        <v>510</v>
+        <v>461</v>
       </c>
       <c r="C16" s="12">
-        <v>459.5</v>
+        <v>743</v>
       </c>
       <c r="D16" s="12">
-        <v>520</v>
+        <v>748</v>
       </c>
       <c r="E16" s="12">
-        <v>426</v>
-      </c>
-      <c r="F16" s="13">
-        <v>-48.5</v>
-      </c>
-      <c r="G16" s="13">
-        <v>-9.5500000000000007</v>
+        <v>460</v>
+      </c>
+      <c r="F16" s="15">
+        <v>283.5</v>
+      </c>
+      <c r="G16" s="15">
+        <v>61.7</v>
       </c>
       <c r="H16" s="14">
-        <v>6.17</v>
+        <v>6.23</v>
       </c>
       <c r="I16" s="15">
-        <v>4.22</v>
+        <v>0.99</v>
       </c>
       <c r="J16" s="15">
-        <v>40.700000000000003</v>
+        <v>23.5</v>
       </c>
       <c r="K16" s="14">
-        <v>62.96</v>
+        <v>6.23</v>
       </c>
       <c r="L16" s="15">
-        <v>31.8</v>
+        <v>23.5</v>
       </c>
       <c r="M16" s="14">
-        <v>6.17</v>
+        <v>6.23</v>
       </c>
       <c r="N16" s="15">
-        <v>4.22</v>
+        <v>0.99</v>
       </c>
       <c r="O16" s="15">
-        <v>40.700000000000003</v>
+        <v>23.5</v>
       </c>
       <c r="P16" s="14">
-        <v>62.96</v>
+        <v>6.23</v>
       </c>
       <c r="Q16" s="15">
-        <v>31.8</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>45597</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>17</v>
+        <v>45627</v>
+      </c>
+      <c r="B17" s="6">
+        <v>510</v>
+      </c>
+      <c r="C17" s="6">
+        <v>459.5</v>
+      </c>
+      <c r="D17" s="6">
+        <v>520</v>
+      </c>
+      <c r="E17" s="6">
+        <v>426</v>
+      </c>
+      <c r="F17" s="9">
+        <v>-48.5</v>
+      </c>
+      <c r="G17" s="9">
+        <v>-9.5500000000000007</v>
       </c>
       <c r="H17" s="8">
-        <v>5.92</v>
-      </c>
-      <c r="I17" s="9">
-        <v>6.39</v>
-      </c>
-      <c r="J17" s="9">
-        <v>31.6</v>
+        <v>6.17</v>
+      </c>
+      <c r="I17" s="7">
+        <v>4.22</v>
+      </c>
+      <c r="J17" s="7">
+        <v>40.700000000000003</v>
       </c>
       <c r="K17" s="8">
-        <v>56.79</v>
-      </c>
-      <c r="L17" s="9">
-        <v>30.8</v>
+        <v>62.96</v>
+      </c>
+      <c r="L17" s="7">
+        <v>31.8</v>
       </c>
       <c r="M17" s="8">
-        <v>5.92</v>
-      </c>
-      <c r="N17" s="9">
-        <v>6.39</v>
-      </c>
-      <c r="O17" s="9">
-        <v>31.6</v>
+        <v>6.17</v>
+      </c>
+      <c r="N17" s="7">
+        <v>4.22</v>
+      </c>
+      <c r="O17" s="7">
+        <v>40.700000000000003</v>
       </c>
       <c r="P17" s="8">
-        <v>56.79</v>
-      </c>
-      <c r="Q17" s="9">
-        <v>30.8</v>
+        <v>62.96</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>31.8</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>17</v>
@@ -2134,31 +2135,31 @@
         <v>17</v>
       </c>
       <c r="H18" s="14">
-        <v>5.57</v>
+        <v>5.92</v>
       </c>
       <c r="I18" s="15">
-        <v>1.97</v>
+        <v>6.39</v>
       </c>
       <c r="J18" s="15">
-        <v>19.5</v>
+        <v>31.6</v>
       </c>
       <c r="K18" s="14">
-        <v>50.87</v>
+        <v>56.79</v>
       </c>
       <c r="L18" s="15">
         <v>30.8</v>
       </c>
       <c r="M18" s="14">
-        <v>5.57</v>
+        <v>5.92</v>
       </c>
       <c r="N18" s="15">
-        <v>1.97</v>
+        <v>6.39</v>
       </c>
       <c r="O18" s="15">
-        <v>19.5</v>
+        <v>31.6</v>
       </c>
       <c r="P18" s="14">
-        <v>50.87</v>
+        <v>56.79</v>
       </c>
       <c r="Q18" s="15">
         <v>30.8</v>
@@ -2166,7 +2167,7 @@
     </row>
     <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>17</v>
@@ -2187,39 +2188,39 @@
         <v>17</v>
       </c>
       <c r="H19" s="8">
-        <v>5.46</v>
-      </c>
-      <c r="I19" s="9">
-        <v>2.56</v>
-      </c>
-      <c r="J19" s="9">
-        <v>42.2</v>
+        <v>5.57</v>
+      </c>
+      <c r="I19" s="7">
+        <v>1.97</v>
+      </c>
+      <c r="J19" s="7">
+        <v>19.5</v>
       </c>
       <c r="K19" s="8">
-        <v>45.3</v>
-      </c>
-      <c r="L19" s="9">
-        <v>32.299999999999997</v>
+        <v>50.87</v>
+      </c>
+      <c r="L19" s="7">
+        <v>30.8</v>
       </c>
       <c r="M19" s="8">
-        <v>5.46</v>
-      </c>
-      <c r="N19" s="9">
-        <v>2.56</v>
-      </c>
-      <c r="O19" s="9">
-        <v>42.2</v>
+        <v>5.57</v>
+      </c>
+      <c r="N19" s="7">
+        <v>1.97</v>
+      </c>
+      <c r="O19" s="7">
+        <v>19.5</v>
       </c>
       <c r="P19" s="8">
-        <v>45.3</v>
-      </c>
-      <c r="Q19" s="9">
-        <v>32.299999999999997</v>
+        <v>50.87</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>30.8</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>17</v>
@@ -2240,39 +2241,39 @@
         <v>17</v>
       </c>
       <c r="H20" s="14">
-        <v>5.32</v>
+        <v>5.46</v>
       </c>
       <c r="I20" s="15">
-        <v>2.97</v>
+        <v>2.56</v>
       </c>
       <c r="J20" s="15">
-        <v>29.2</v>
+        <v>42.2</v>
       </c>
       <c r="K20" s="14">
-        <v>39.840000000000003</v>
+        <v>45.3</v>
       </c>
       <c r="L20" s="15">
-        <v>31</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="M20" s="14">
-        <v>5.32</v>
+        <v>5.46</v>
       </c>
       <c r="N20" s="15">
-        <v>2.97</v>
+        <v>2.56</v>
       </c>
       <c r="O20" s="15">
-        <v>29.2</v>
+        <v>42.2</v>
       </c>
       <c r="P20" s="14">
-        <v>39.840000000000003</v>
+        <v>45.3</v>
       </c>
       <c r="Q20" s="15">
-        <v>31</v>
+        <v>32.299999999999997</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>17</v>
@@ -2293,39 +2294,39 @@
         <v>17</v>
       </c>
       <c r="H21" s="8">
-        <v>5.17</v>
+        <v>5.32</v>
       </c>
       <c r="I21" s="7">
-        <v>-6.51</v>
-      </c>
-      <c r="J21" s="9">
-        <v>20.2</v>
+        <v>2.97</v>
+      </c>
+      <c r="J21" s="7">
+        <v>29.2</v>
       </c>
       <c r="K21" s="8">
-        <v>34.520000000000003</v>
-      </c>
-      <c r="L21" s="9">
-        <v>31.3</v>
+        <v>39.840000000000003</v>
+      </c>
+      <c r="L21" s="7">
+        <v>31</v>
       </c>
       <c r="M21" s="8">
-        <v>5.17</v>
+        <v>5.32</v>
       </c>
       <c r="N21" s="7">
-        <v>-6.51</v>
-      </c>
-      <c r="O21" s="9">
-        <v>20.2</v>
+        <v>2.97</v>
+      </c>
+      <c r="O21" s="7">
+        <v>29.2</v>
       </c>
       <c r="P21" s="8">
-        <v>34.520000000000003</v>
-      </c>
-      <c r="Q21" s="9">
-        <v>31.3</v>
+        <v>39.840000000000003</v>
+      </c>
+      <c r="Q21" s="7">
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>17</v>
@@ -2346,39 +2347,39 @@
         <v>17</v>
       </c>
       <c r="H22" s="14">
-        <v>5.53</v>
-      </c>
-      <c r="I22" s="15">
-        <v>15.4</v>
+        <v>5.17</v>
+      </c>
+      <c r="I22" s="13">
+        <v>-6.51</v>
       </c>
       <c r="J22" s="15">
-        <v>52.7</v>
+        <v>20.2</v>
       </c>
       <c r="K22" s="14">
-        <v>29.35</v>
+        <v>34.520000000000003</v>
       </c>
       <c r="L22" s="15">
-        <v>33.5</v>
+        <v>31.3</v>
       </c>
       <c r="M22" s="14">
-        <v>5.53</v>
-      </c>
-      <c r="N22" s="15">
-        <v>15.4</v>
+        <v>5.17</v>
+      </c>
+      <c r="N22" s="13">
+        <v>-6.51</v>
       </c>
       <c r="O22" s="15">
-        <v>52.7</v>
+        <v>20.2</v>
       </c>
       <c r="P22" s="14">
-        <v>29.35</v>
+        <v>34.520000000000003</v>
       </c>
       <c r="Q22" s="15">
-        <v>33.5</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>17</v>
@@ -2399,39 +2400,39 @@
         <v>17</v>
       </c>
       <c r="H23" s="8">
-        <v>4.79</v>
-      </c>
-      <c r="I23" s="9">
-        <v>7.93</v>
-      </c>
-      <c r="J23" s="9">
-        <v>29</v>
+        <v>5.53</v>
+      </c>
+      <c r="I23" s="7">
+        <v>15.4</v>
+      </c>
+      <c r="J23" s="7">
+        <v>52.7</v>
       </c>
       <c r="K23" s="8">
-        <v>23.83</v>
-      </c>
-      <c r="L23" s="9">
-        <v>29.7</v>
+        <v>29.35</v>
+      </c>
+      <c r="L23" s="7">
+        <v>33.5</v>
       </c>
       <c r="M23" s="8">
-        <v>4.79</v>
-      </c>
-      <c r="N23" s="9">
-        <v>7.93</v>
-      </c>
-      <c r="O23" s="9">
-        <v>29</v>
+        <v>5.53</v>
+      </c>
+      <c r="N23" s="7">
+        <v>15.4</v>
+      </c>
+      <c r="O23" s="7">
+        <v>52.7</v>
       </c>
       <c r="P23" s="8">
-        <v>23.83</v>
-      </c>
-      <c r="Q23" s="9">
-        <v>29.7</v>
+        <v>29.35</v>
+      </c>
+      <c r="Q23" s="7">
+        <v>33.5</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>17</v>
@@ -2452,39 +2453,39 @@
         <v>17</v>
       </c>
       <c r="H24" s="14">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="I24" s="13">
-        <v>-8.42</v>
+        <v>4.79</v>
+      </c>
+      <c r="I24" s="15">
+        <v>7.93</v>
       </c>
       <c r="J24" s="15">
-        <v>21.1</v>
+        <v>29</v>
       </c>
       <c r="K24" s="14">
-        <v>19.04</v>
+        <v>23.83</v>
       </c>
       <c r="L24" s="15">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="M24" s="14">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="N24" s="13">
-        <v>-8.42</v>
+        <v>4.79</v>
+      </c>
+      <c r="N24" s="15">
+        <v>7.93</v>
       </c>
       <c r="O24" s="15">
-        <v>21.1</v>
+        <v>29</v>
       </c>
       <c r="P24" s="14">
-        <v>19.04</v>
+        <v>23.83</v>
       </c>
       <c r="Q24" s="15">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>17</v>
@@ -2505,39 +2506,39 @@
         <v>17</v>
       </c>
       <c r="H25" s="8">
-        <v>4.8499999999999996</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="I25" s="9">
-        <v>2.99</v>
-      </c>
-      <c r="J25" s="9">
-        <v>31.8</v>
+        <v>-8.42</v>
+      </c>
+      <c r="J25" s="7">
+        <v>21.1</v>
       </c>
       <c r="K25" s="8">
-        <v>14.6</v>
-      </c>
-      <c r="L25" s="9">
-        <v>32.799999999999997</v>
+        <v>19.04</v>
+      </c>
+      <c r="L25" s="7">
+        <v>29.9</v>
       </c>
       <c r="M25" s="8">
-        <v>4.8499999999999996</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="N25" s="9">
-        <v>2.99</v>
-      </c>
-      <c r="O25" s="9">
-        <v>31.8</v>
+        <v>-8.42</v>
+      </c>
+      <c r="O25" s="7">
+        <v>21.1</v>
       </c>
       <c r="P25" s="8">
-        <v>14.6</v>
-      </c>
-      <c r="Q25" s="9">
-        <v>32.799999999999997</v>
+        <v>19.04</v>
+      </c>
+      <c r="Q25" s="7">
+        <v>29.9</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>17</v>
@@ -2558,39 +2559,39 @@
         <v>17</v>
       </c>
       <c r="H26" s="14">
-        <v>4.7</v>
-      </c>
-      <c r="I26" s="13">
-        <v>-6.78</v>
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="I26" s="15">
+        <v>2.99</v>
       </c>
       <c r="J26" s="15">
-        <v>35</v>
+        <v>31.8</v>
       </c>
       <c r="K26" s="14">
-        <v>9.75</v>
+        <v>14.6</v>
       </c>
       <c r="L26" s="15">
-        <v>33.4</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="M26" s="14">
-        <v>4.7</v>
-      </c>
-      <c r="N26" s="13">
-        <v>-6.78</v>
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="N26" s="15">
+        <v>2.99</v>
       </c>
       <c r="O26" s="15">
-        <v>35</v>
+        <v>31.8</v>
       </c>
       <c r="P26" s="14">
-        <v>9.75</v>
+        <v>14.6</v>
       </c>
       <c r="Q26" s="15">
-        <v>33.4</v>
+        <v>32.799999999999997</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>17</v>
@@ -2611,39 +2612,39 @@
         <v>17</v>
       </c>
       <c r="H27" s="8">
-        <v>5.05</v>
+        <v>4.7</v>
       </c>
       <c r="I27" s="9">
-        <v>15</v>
-      </c>
-      <c r="J27" s="9">
-        <v>31.8</v>
+        <v>-6.78</v>
+      </c>
+      <c r="J27" s="7">
+        <v>35</v>
       </c>
       <c r="K27" s="8">
-        <v>5.05</v>
-      </c>
-      <c r="L27" s="9">
-        <v>31.8</v>
+        <v>9.75</v>
+      </c>
+      <c r="L27" s="7">
+        <v>33.4</v>
       </c>
       <c r="M27" s="8">
-        <v>5.05</v>
+        <v>4.7</v>
       </c>
       <c r="N27" s="9">
-        <v>15</v>
-      </c>
-      <c r="O27" s="9">
-        <v>31.8</v>
+        <v>-6.78</v>
+      </c>
+      <c r="O27" s="7">
+        <v>35</v>
       </c>
       <c r="P27" s="8">
-        <v>5.05</v>
-      </c>
-      <c r="Q27" s="9">
-        <v>31.8</v>
+        <v>9.75</v>
+      </c>
+      <c r="Q27" s="7">
+        <v>33.4</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>17</v>
@@ -2664,86 +2665,139 @@
         <v>17</v>
       </c>
       <c r="H28" s="14">
-        <v>4.3899999999999997</v>
-      </c>
-      <c r="I28" s="13">
-        <v>-2.52</v>
+        <v>5.05</v>
+      </c>
+      <c r="I28" s="15">
+        <v>15</v>
       </c>
       <c r="J28" s="15">
-        <v>14.5</v>
+        <v>31.8</v>
       </c>
       <c r="K28" s="14">
-        <v>47.79</v>
+        <v>5.05</v>
       </c>
       <c r="L28" s="15">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="M28" s="14">
-        <v>4.3899999999999997</v>
-      </c>
-      <c r="N28" s="13">
-        <v>-2.52</v>
+        <v>5.05</v>
+      </c>
+      <c r="N28" s="15">
+        <v>15</v>
       </c>
       <c r="O28" s="15">
-        <v>14.5</v>
+        <v>31.8</v>
       </c>
       <c r="P28" s="14">
-        <v>47.79</v>
+        <v>5.05</v>
       </c>
       <c r="Q28" s="15">
-        <v>32</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
+        <v>45261</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H29" s="8">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="I29" s="9">
+        <v>-2.52</v>
+      </c>
+      <c r="J29" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="K29" s="8">
+        <v>47.79</v>
+      </c>
+      <c r="L29" s="7">
+        <v>32</v>
+      </c>
+      <c r="M29" s="8">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="N29" s="9">
+        <v>-2.52</v>
+      </c>
+      <c r="O29" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="P29" s="8">
+        <v>47.79</v>
+      </c>
+      <c r="Q29" s="7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="11">
         <v>45231</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H29" s="8">
+      <c r="B30" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H30" s="14">
         <v>4.5</v>
       </c>
-      <c r="I29" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="9">
+      <c r="I30" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="15">
         <v>25.1</v>
       </c>
-      <c r="K29" s="8">
+      <c r="K30" s="14">
         <v>43.4</v>
       </c>
-      <c r="L29" s="9">
+      <c r="L30" s="15">
         <v>34.1</v>
       </c>
-      <c r="M29" s="8">
+      <c r="M30" s="14">
         <v>4.5</v>
       </c>
-      <c r="N29" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="O29" s="9">
+      <c r="N30" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="O30" s="15">
         <v>25.1</v>
       </c>
-      <c r="P29" s="8">
+      <c r="P30" s="14">
         <v>43.4</v>
       </c>
-      <c r="Q29" s="9">
+      <c r="Q30" s="15">
         <v>34.1</v>
       </c>
     </row>
